--- a/data/trans_dic/P44D-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P44D-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -678,22 +678,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,92</t>
+          <t>0,0; 73,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,11; 45,25</t>
+          <t>7,33; 43,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 11,61</t>
+          <t>2,77; 11,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,53; 71,1</t>
+          <t>9,89; 76,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -703,22 +703,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 14,43</t>
+          <t>2,67; 14,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,96; 61,13</t>
+          <t>11,81; 58,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 28,07</t>
+          <t>2,97; 29,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 10,38</t>
+          <t>3,17; 10,44</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,34</t>
+          <t>0,0; 45,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,37 +798,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 20,32</t>
+          <t>4,1; 21,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,76</t>
+          <t>0,0; 32,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,78</t>
+          <t>0,0; 76,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 16,73</t>
+          <t>2,86; 14,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,65; 28,86</t>
+          <t>2,84; 26,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,67</t>
+          <t>0,0; 27,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,78; 15,92</t>
+          <t>4,21; 15,02</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,2</t>
+          <t>0,0; 50,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 35,32</t>
+          <t>3,78; 34,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 13,87</t>
+          <t>2,45; 13,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,27 +918,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,62</t>
+          <t>0,0; 32,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,16; 17,98</t>
+          <t>4,95; 17,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,12</t>
+          <t>0,0; 27,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 25,36</t>
+          <t>2,72; 24,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,8; 13,02</t>
+          <t>4,49; 13,15</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,29</t>
+          <t>0,0; 76,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,2; 40,44</t>
+          <t>7,26; 37,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,67; 18,26</t>
+          <t>4,03; 18,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,43</t>
+          <t>0,0; 32,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,38; 42,55</t>
+          <t>5,47; 43,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,86; 20,11</t>
+          <t>7,46; 19,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,02; 42,64</t>
+          <t>4,06; 46,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,67; 31,26</t>
+          <t>9,14; 34,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,83; 16,78</t>
+          <t>7,07; 16,25</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,49</t>
+          <t>0,0; 65,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,27</t>
+          <t>0,0; 23,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1143,22 +1143,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,23</t>
+          <t>0,0; 12,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,4</t>
+          <t>0,0; 31,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,93</t>
+          <t>0,0; 80,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 13,49</t>
+          <t>1,48; 14,07</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,48</t>
+          <t>0,0; 40,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,8</t>
+          <t>0,0; 44,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,24; 11,54</t>
+          <t>1,23; 12,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1253,22 +1253,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,27</t>
+          <t>0,0; 8,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,48</t>
+          <t>0,0; 27,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,33</t>
+          <t>0,0; 26,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,04; 7,21</t>
+          <t>1,27; 8,13</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,64</t>
+          <t>0,0; 47,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,65; 23,85</t>
+          <t>2,67; 24,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,31; 26,23</t>
+          <t>12,73; 25,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20,87; 68,54</t>
+          <t>20,93; 70,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,11</t>
+          <t>0,0; 22,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,08; 11,89</t>
+          <t>4,1; 12,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,31; 51,35</t>
+          <t>17,12; 51,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,11; 18,93</t>
+          <t>4,33; 19,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,17; 17,41</t>
+          <t>9,26; 17,14</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -1453,42 +1453,42 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,94; 33,82</t>
+          <t>4,11; 35,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,43; 8,99</t>
+          <t>4,04; 12,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,67</t>
+          <t>0,0; 44,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,58; 70,01</t>
+          <t>9,51; 68,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,99; 8,58</t>
+          <t>2,67; 8,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,22</t>
+          <t>0,0; 16,78</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,39; 40,52</t>
+          <t>11,3; 40,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,95; 7,4</t>
+          <t>4,21; 9,18</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,06; 22,96</t>
+          <t>6,58; 22,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,24; 20,88</t>
+          <t>9,12; 20,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,79; 10,61</t>
+          <t>7,54; 12,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,95; 27,58</t>
+          <t>10,57; 27,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,94; 19,58</t>
+          <t>6,02; 19,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,73; 9,18</t>
+          <t>5,78; 9,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,57; 21,61</t>
+          <t>10,35; 21,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,34; 17,88</t>
+          <t>9,02; 17,84</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,63; 9,02</t>
+          <t>7,24; 10,04</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>6811</t>
         </is>
       </c>
     </row>
@@ -1861,22 +1861,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5072</t>
+          <t>0; 5083</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1195; 10570</t>
+          <t>1711; 10098</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1521; 8516</t>
+          <t>2035; 8669</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1055; 7871</t>
+          <t>1095; 8520</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1886,22 +1886,22 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>985; 5150</t>
+          <t>978; 5415</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2156; 11019</t>
+          <t>2129; 10537</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1222; 11030</t>
+          <t>1169; 11474</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3108; 11316</t>
+          <t>3496; 11503</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>9696</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 10211</t>
+          <t>0; 10861</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2034,37 +2034,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2425; 12915</t>
+          <t>2712; 14147</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6074</t>
+          <t>0; 6593</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4541</t>
+          <t>0; 4288</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1174; 6612</t>
+          <t>1207; 6240</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2072; 12852</t>
+          <t>1267; 11675</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4488</t>
+          <t>0; 4604</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4924; 16406</t>
+          <t>4562; 16259</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3672</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9126</t>
+          <t>9015</t>
         </is>
       </c>
     </row>
@@ -2187,17 +2187,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4628</t>
+          <t>0; 4626</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703; 6449</t>
+          <t>690; 6240</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1277; 7880</t>
+          <t>1362; 7495</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2207,27 +2207,27 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6923</t>
+          <t>0; 5498</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2877; 10024</t>
+          <t>2829; 10023</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4321</t>
+          <t>0; 5821</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>942; 8952</t>
+          <t>961; 8535</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5403; 14658</t>
+          <t>5065; 14835</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7715</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12869</t>
+          <t>14000</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 8112</t>
+          <t>0; 8361</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1860; 10450</t>
+          <t>1876; 9812</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2471; 9655</t>
+          <t>2413; 11263</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5061</t>
+          <t>0; 4799</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1099; 8688</t>
+          <t>1118; 8853</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4652; 11898</t>
+          <t>4791; 12246</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1031; 10925</t>
+          <t>1040; 11925</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4012; 14461</t>
+          <t>4228; 15789</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8774; 18796</t>
+          <t>8765; 20154</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>419</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1430</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4188</t>
+          <t>0; 4140</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3253</t>
+          <t>0; 3219</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2538,22 +2538,22 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1984</t>
+          <t>0; 1829</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5069</t>
+          <t>0; 4103</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3943</t>
+          <t>0; 3984</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>400; 3618</t>
+          <t>418; 3977</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2676,17 +2676,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4260</t>
+          <t>0; 4175</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4549</t>
+          <t>0; 4650</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>481; 4495</t>
+          <t>467; 4693</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2701,22 +2701,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 2220</t>
+          <t>0; 2672</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4717</t>
+          <t>0; 4566</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4620</t>
+          <t>0; 5106</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>724; 5009</t>
+          <t>871; 5596</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20443</t>
+          <t>22864</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8512</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>28955</t>
+          <t>33171</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 8563</t>
+          <t>0; 8591</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1059; 9554</t>
+          <t>1068; 9765</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13227; 28178</t>
+          <t>15750; 31859</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4730; 15534</t>
+          <t>4745; 15997</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 6800</t>
+          <t>0; 6418</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4675; 13641</t>
+          <t>5557; 16387</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7034; 20868</t>
+          <t>6957; 20924</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2125; 12920</t>
+          <t>2955; 13454</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>20359; 38681</t>
+          <t>23994; 44417</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>10533</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6932</t>
+          <t>7883</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>16610</t>
+          <t>18416</t>
         </is>
       </c>
     </row>
@@ -3007,42 +3007,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1003; 8617</t>
+          <t>1047; 9096</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1592; 33567</t>
+          <t>5807; 17753</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 6571</t>
+          <t>0; 6636</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1055; 7710</t>
+          <t>1048; 7579</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3891; 11161</t>
+          <t>3965; 12719</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 6392</t>
+          <t>0; 7050</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4157; 14786</t>
+          <t>4122; 14754</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4774; 37271</t>
+          <t>12319; 26853</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>51933</t>
+          <t>56373</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35281</t>
+          <t>38506</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>87214</t>
+          <t>94879</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>7959; 25874</t>
+          <t>7418; 25094</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>14556; 32903</t>
+          <t>14371; 32738</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21733; 82658</t>
+          <t>43276; 70065</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11935; 30070</t>
+          <t>11527; 29719</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>6460; 21299</t>
+          <t>6545; 21487</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27459; 44017</t>
+          <t>30610; 49095</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23433; 47920</t>
+          <t>22938; 48677</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>24879; 47632</t>
+          <t>24014; 47511</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>45666; 113496</t>
+          <t>79876; 110878</t>
         </is>
       </c>
     </row>
